--- a/ablation_results.xlsx
+++ b/ablation_results.xlsx
@@ -9,10 +9,20 @@
   <sheets>
     <sheet name="ConstrainedGoToLocal_1c" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ConstrainedGoToObjDoor_1c" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ConstrainedOpenDoor_1c" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ConstrainedPickupDist_1c" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ConstrainedActionObjDoor_1c" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ConstrainedOpenDoor_1c" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ConstrainedOpenDoorLoc_1c" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ConstrainedOpenDoorsOrder_1c" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ConstrainedPickupDist_1c" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ConstrainedGoToOpen_1c" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ConstrainedOpenDoorsOrder_1c" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ConstrainedGoToObjDoor_2c" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ConstrainedActionObjDoor_2c" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ConstrainedGoToLocal_2c" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ConstrainedOpenDoor_2c" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ConstrainedGoToOpen_2c" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ConstrainedPickupDist_2c" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ConstrainedOpenDoorsOrder_2c" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ConstrainedOpenDoorLoc_2c" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +453,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Delta G</t>
+          <t>Delta Theta</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -478,32 +488,32 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Goal Adapter Only</t>
+          <t>Avg Steps Global + Goal Adapter</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Goal Adapter Only</t>
+          <t>Success Prob Global + Goal Adapter</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Goal Adapter Only</t>
+          <t>Avg Viols Global + Goal Adapter</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Constraint Adapter Only</t>
+          <t>Avg Steps Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Constraint Adapter Only</t>
+          <t>Success Prob Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Constraint Adapter Only</t>
+          <t>Avg Viols Global + Constraint Adapter</t>
         </is>
       </c>
     </row>
@@ -518,58 +528,58 @@
         <v>300</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.48 ± 103.87</t>
+          <t>99.12 ± 110.31</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.03 ± 0.30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>74.22 ± 94.37</t>
+          <t>116.65 ± 107.21</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.68 ± 2.53</t>
+          <t>10.64 ± 20.95</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>92.94 ± 117.10</t>
+          <t>79.70 ± 98.50</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.07 ± 0.45</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>71.56 ± 92.95</t>
+          <t>99.08 ± 97.91</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.84 ± 2.75</t>
+          <t>4.15 ± 12.00</t>
         </is>
       </c>
     </row>
@@ -584,58 +594,58 @@
         <v>300</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80.22 ± 106.71</t>
+          <t>79.69 ± 104.01</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.30</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>113.88 ± 109.87</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7.55 ± 15.07</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>80.83 ± 106.07</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>0.84</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>80.21 ± 107.55</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.95 ± 2.79</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>86.63 ± 108.50</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.86</v>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.03 ± 0.30</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>79.34 ± 98.09</t>
+          <t>101.79 ± 104.59</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.05 ± 4.53</t>
+          <t>5.94 ± 14.04</t>
         </is>
       </c>
     </row>
@@ -650,58 +660,58 @@
         <v>300</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.56 ± 101.33</t>
+          <t>100.77 ± 115.51</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>102.66 ± 104.03</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.86</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>90.33 ± 98.34</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.92</v>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.39 ± 1.55</t>
+          <t>6.07 ± 9.44</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>73.23 ± 102.68</t>
+          <t>99.35 ± 110.30</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.09 ± 0.51</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>93.20 ± 99.44</t>
+          <t>109.20 ± 102.79</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.37 ± 1.12</t>
+          <t>4.21 ± 7.48</t>
         </is>
       </c>
     </row>
@@ -716,15 +726,15 @@
         <v>300</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82.81 ± 106.45</t>
+          <t>85.76 ± 104.81</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -733,41 +743,41 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>101.21 ± 107.69</t>
+          <t>124.14 ± 111.90</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.33 ± 1.27</t>
+          <t>7.44 ± 15.81</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.31 ± 114.73</t>
+          <t>81.25 ± 103.45</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.09 ± 0.55</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>101.78 ± 110.91</t>
+          <t>117.79 ± 112.20</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.56 ± 1.47</t>
+          <t>4.07 ± 7.65</t>
         </is>
       </c>
     </row>
@@ -782,15 +792,15 @@
         <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>85.32 ± 90.33</t>
+          <t>85.06 ± 94.87</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -799,41 +809,41 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>115.02 ± 109.44</t>
+          <t>144.14 ± 113.85</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.01 ± 6.69</t>
+          <t>6.16 ± 12.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>91.85 ± 99.72</t>
+          <t>93.84 ± 95.57</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.01 ± 0.10</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>124.32 ± 113.25</t>
+          <t>136.51 ± 109.56</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.56 ± 2.45</t>
+          <t>3.50 ± 6.12</t>
         </is>
       </c>
     </row>
@@ -848,15 +858,15 @@
         <v>300</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>94.32 ± 100.62</t>
+          <t>105.04 ± 115.03</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -865,41 +875,41 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>117.81 ± 117.24</t>
+          <t>164.28 ± 113.00</t>
         </is>
       </c>
       <c r="I7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9.22 ± 11.92</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>108.90 ± 108.92</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.28</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>130.89 ± 109.49</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>0.78</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.74 ± 3.26</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>106.34 ± 114.44</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>135.19 ± 111.73</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>0.8</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.78 ± 2.19</t>
+          <t>4.08 ± 8.23</t>
         </is>
       </c>
     </row>
@@ -914,54 +924,3306 @@
       <c r="D8" s="1" t="inlineStr"/>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>82.78 ± 101.88</t>
+          <t>92.57 ± 108.08</t>
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.01 ± 0.17</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>96.47 ± 107.30</t>
+          <t>127.62 ± 111.96</t>
         </is>
       </c>
       <c r="I8" s="1" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>7.85 ± 14.88</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>90.64 ± 104.52</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
         <v>0.85</v>
       </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>0.06 ± 0.40</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>115.88 ± 107.12</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>4.33 ± 9.70</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>510.74 ± 425.87</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8.47 ± 11.16</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>588.56 ± 430.30</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>28.71 ± 32.57</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>523.26 ± 436.23</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>10.09 ± 12.71</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>590.95 ± 423.72</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>23.52 ± 30.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>510.74 ± 425.87</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>8.47 ± 11.16</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>588.56 ± 430.30</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>28.71 ± 32.57</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>523.26 ± 436.23</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>10.09 ± 12.71</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>590.95 ± 423.72</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>23.52 ± 30.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>127.90 ± 130.66</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>127.54 ± 114.48</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>23.67 ± 34.31</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>130.36 ± 129.39</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.79 ± 10.34</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>116.53 ± 113.54</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>19.46 ± 28.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>146.64 ± 133.89</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.35 ± 3.38</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>142.24 ± 119.67</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>31.18 ± 41.63</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>144.25 ± 133.43</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.65 ± 12.57</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>126.73 ± 111.84</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>17.79 ± 26.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>137.93 ± 127.34</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>121.60 ± 109.19</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>18.10 ± 23.26</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>139.26 ± 123.99</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.32 ± 1.19</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>116.11 ± 112.26</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>16.46 ± 22.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>122.10 ± 125.78</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.13 ± 1.02</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>146.05 ± 116.46</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>21.50 ± 29.66</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>125.56 ± 126.87</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.25 ± 1.16</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>148.41 ± 120.45</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>18.34 ± 24.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>132.19 ± 118.63</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>155.66 ± 115.50</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>18.29 ± 21.27</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>145.00 ± 121.70</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.13 ± 0.46</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>140.09 ± 111.16</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>14.90 ± 17.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>136.27 ± 119.37</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.30</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>150.03 ± 110.65</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>18.14 ± 23.37</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>182.39 ± 124.42</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.27 ± 2.19</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>154.29 ± 118.45</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>15.48 ± 21.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>133.84 ± 126.31</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>0.10 ± 1.46</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>140.52 ± 115.02</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.74</v>
+      </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>0.68 ± 3.51</t>
+          <t>21.81 ± 30.17</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>91.55 ± 110.19</t>
+          <t>144.47 ± 128.02</t>
         </is>
       </c>
       <c r="L8" s="1" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>0.73 ± 6.78</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>133.69 ± 115.64</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>17.07 ± 23.73</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>632.25 ± 309.98</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>7.43 ± 15.70</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>516.68 ± 338.78</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>33.70 ± 42.31</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>636.23 ± 311.64</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>13.17 ± 28.73</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>545.10 ± 334.52</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>28.93 ± 35.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>518.00 ± 363.36</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12.10 ± 23.19</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>618.43 ± 295.64</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>27.23 ± 34.30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>475.02 ± 374.44</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>18.70 ± 37.65</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>519.57 ± 330.41</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>36.37 ± 48.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>539.75 ± 356.25</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>18.32 ± 37.53</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>602.98 ± 301.90</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30.32 ± 33.65</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>559.93 ± 344.91</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>19.33 ± 35.10</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>626.95 ± 285.94</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>27.28 ± 44.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>669.77 ± 280.58</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>17.92 ± 35.33</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>615.47 ± 289.74</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>31.00 ± 50.76</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>707.28 ± 233.75</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>15.73 ± 36.55</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>633.50 ± 269.34</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>17.70 ± 29.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>572.80 ± 334.86</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>14.87 ± 44.47</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>578.00 ± 312.83</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>27.02 ± 49.25</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>613.75 ± 317.84</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>8.00 ± 25.40</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>606.83 ± 284.82</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>14.33 ± 20.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>586.51 ± 335.26</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>14.13 ± 33.17</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>586.31 ± 310.55</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>29.85 ± 42.74</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>598.44 ± 329.29</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>14.99 ± 33.29</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>586.39 ± 305.60</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>24.92 ± 37.96</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>429.57 ± 417.96</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>19.03 ± 47.71</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>366.07 ± 356.59</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.84</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>23.37 ± 52.67</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>403.73 ± 412.95</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>17.60 ± 36.36</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>455.83 ± 417.09</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>28.97 ± 56.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>424.41 ± 417.36</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>20.29 ± 90.30</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>482.92 ± 422.05</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>31.04 ± 76.39</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>422.32 ± 403.95</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>29.40 ± 94.35</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>437.91 ± 397.43</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>18.32 ± 39.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>487.24 ± 398.64</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>21.26 ± 66.86</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>539.94 ± 413.39</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>40.80 ± 61.75</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>416.95 ± 398.12</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>31.25 ± 89.41</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>521.04 ± 395.90</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>28.81 ± 47.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>483.01 ± 422.18</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>17.23 ± 43.73</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>530.88 ± 399.11</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>29.44 ± 54.99</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>429.69 ± 379.70</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>21.34 ± 60.95</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>511.87 ± 409.35</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20.13 ± 40.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>456.06 ± 415.16</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>19.45 ± 64.85</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>479.95 ± 404.55</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>31.16 ± 62.46</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>418.17 ± 398.98</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>24.90 ± 74.26</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>481.66 ± 406.59</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>24.06 ± 46.86</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>274.22 ± 206.70</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.73 ± 5.35</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>331.77 ± 194.50</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>42.47 ± 39.04</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>382.51 ± 194.85</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>21.93 ± 51.78</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>313.51 ± 200.44</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>30.90 ± 32.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>310.72 ± 207.58</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3.87 ± 13.05</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>372.30 ± 194.64</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>49.27 ± 45.39</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>414.22 ± 178.40</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>26.41 ± 65.00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>356.43 ± 196.31</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>37.44 ± 35.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>255.08 ± 205.78</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3.44 ± 7.76</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>280.15 ± 194.78</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>24.82 ± 25.13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>285.61 ± 220.89</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>15.26 ± 34.81</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>303.60 ± 191.87</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>21.21 ± 19.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>308.24 ± 209.05</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2.64 ± 4.19</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>329.59 ± 207.54</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>27.80 ± 24.35</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>382.04 ± 199.73</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>18.92 ± 39.25</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>352.27 ± 190.46</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>27.13 ± 24.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>306.30 ± 190.99</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2.06 ± 5.41</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>344.78 ± 179.09</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>22.54 ± 22.43</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>368.84 ± 206.59</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>12.39 ± 33.71</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>308.63 ± 200.17</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>16.47 ± 15.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>379.58 ± 182.91</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.37 ± 5.94</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>325.90 ± 190.72</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>20.91 ± 20.75</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>388.51 ± 193.80</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>13.51 ± 50.33</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>378.63 ± 172.81</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>23.32 ± 24.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>305.69 ± 204.47</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>2.85 ± 7.56</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>330.75 ± 195.66</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>31.30 ± 32.73</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>370.29 ± 203.48</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.32</v>
+      </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>18.07 ± 47.39</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>100.90 ± 107.14</t>
+          <t>335.51 ± 194.31</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>26.08 ± 27.10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>336.43 ± 469.09</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.11 ± 0.60</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>479.65 ± 458.40</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>51.45 ± 64.03</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>415.31 ± 471.67</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.28 ± 1.29</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>539.25 ± 484.11</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>58.65 ± 83.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>322.81 ± 416.19</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>0.85</v>
       </c>
-      <c r="P8" s="1" t="inlineStr">
-        <is>
-          <t>0.69 ± 2.66</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.41 ± 2.93</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>514.14 ± 456.89</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>45.83 ± 60.33</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>461.20 ± 461.15</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.71</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>574.30 ± 468.49</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>55.50 ± 74.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>307.20 ± 374.41</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>524.56 ± 450.77</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>34.89 ± 43.86</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>452.28 ± 452.05</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>682.20 ± 477.29</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>44.64 ± 58.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>290.74 ± 315.45</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.31</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>652.62 ± 445.76</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>30.20 ± 28.88</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>539.21 ± 457.91</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.40 ± 2.84</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>610.53 ± 480.13</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>25.99 ± 33.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>308.55 ± 318.13</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>676.05 ± 459.13</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>26.17 ± 35.17</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>569.64 ± 480.73</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.15 ± 0.90</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>743.36 ± 465.78</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>30.57 ± 46.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>313.15 ± 383.50</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>0.12 ± 1.36</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>569.40 ± 461.08</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>37.71 ± 49.37</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>487.53 ± 468.37</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>0.19 ± 1.49</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>629.93 ± 480.92</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>43.07 ± 63.30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>503.97 ± 372.88</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.90 ± 6.84</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>574.27 ± 326.35</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>22.10 ± 35.26</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>543.63 ± 355.86</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>11.35 ± 59.01</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>567.69 ± 334.38</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>38.02 ± 88.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>497.70 ± 372.35</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>16.94 ± 56.17</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>532.74 ± 336.00</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15.01 ± 23.24</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>590.85 ± 325.32</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>21.14 ± 93.31</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>566.25 ± 336.28</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20.49 ± 35.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>455.71 ± 382.63</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>13.63 ± 48.76</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>529.19 ± 334.92</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>18.25 ± 36.42</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>548.87 ± 355.81</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>12.24 ± 32.24</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>522.48 ± 337.11</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>19.71 ± 59.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>444.31 ± 373.95</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6.23 ± 21.24</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>490.06 ± 331.14</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>12.23 ± 18.51</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>544.92 ± 352.18</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5.41 ± 15.58</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>523.07 ± 329.72</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>19.36 ± 47.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>450.37 ± 373.13</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6.76 ± 20.02</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>530.27 ± 327.03</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14.64 ± 36.01</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>518.06 ± 355.14</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4.06 ± 10.78</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>580.81 ± 303.03</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>17.87 ± 52.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>470.41 ± 375.85</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>9.29 ± 36.24</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>531.31 ± 332.19</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>16.45 ± 31.01</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>549.27 ± 349.85</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>10.84 ± 52.48</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>552.06 ± 329.26</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>23.09 ± 60.07</t>
         </is>
       </c>
     </row>
@@ -997,7 +4259,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Delta G</t>
+          <t>Delta Theta</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1032,32 +4294,32 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Goal Adapter Only</t>
+          <t>Avg Steps Global + Goal Adapter</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Goal Adapter Only</t>
+          <t>Success Prob Global + Goal Adapter</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Goal Adapter Only</t>
+          <t>Avg Viols Global + Goal Adapter</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Constraint Adapter Only</t>
+          <t>Avg Steps Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Constraint Adapter Only</t>
+          <t>Success Prob Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Constraint Adapter Only</t>
+          <t>Avg Viols Global + Constraint Adapter</t>
         </is>
       </c>
     </row>
@@ -1074,15 +4336,15 @@
         <v>300</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.46 ± 93.33</t>
+          <t>87.83 ± 83.61</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1091,20 +4353,20 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>146.35 ± 112.61</t>
+          <t>154.84 ± 102.18</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.51 ± 17.09</t>
+          <t>4.11 ± 6.95</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>85.55 ± 99.59</t>
+          <t>96.94 ± 98.17</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -1112,20 +4374,20 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.10 ± 0.30</t>
+          <t>0.05 ± 0.22</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>117.26 ± 98.84</t>
+          <t>162.13 ± 112.17</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.50 ± 6.87</t>
+          <t>3.18 ± 6.10</t>
         </is>
       </c>
     </row>
@@ -1142,15 +4404,15 @@
         <v>300</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>62.82 ± 83.99</t>
+          <t>73.83 ± 90.38</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1159,7 +4421,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>144.95 ± 115.04</t>
+          <t>135.50 ± 107.64</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -1167,33 +4429,33 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.66 ± 11.01</t>
+          <t>4.12 ± 7.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>113.83 ± 113.69</t>
+          <t>104.93 ± 102.60</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.26 ± 1.10</t>
+          <t>0.14 ± 0.49</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>109.91 ± 101.79</t>
+          <t>120.89 ± 111.53</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.01 ± 7.13</t>
+          <t>2.45 ± 5.68</t>
         </is>
       </c>
     </row>
@@ -1210,15 +4472,15 @@
         <v>300</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>82.61 ± 96.57</t>
+          <t>63.86 ± 77.67</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1227,41 +4489,41 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>155.62 ± 116.93</t>
+          <t>136.52 ± 106.86</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.17 ± 12.26</t>
+          <t>5.29 ± 11.22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>138.75 ± 119.31</t>
+          <t>100.63 ± 103.30</t>
         </is>
       </c>
       <c r="L4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.13 ± 0.76</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>143.55 ± 117.13</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>0.72</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1.58 ± 8.22</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>102.90 ± 103.93</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>0.87</v>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3.06 ± 5.55</t>
+          <t>1.98 ± 4.28</t>
         </is>
       </c>
     </row>
@@ -1278,15 +4540,15 @@
         <v>300</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>78.31 ± 85.81</t>
+          <t>78.41 ± 77.68</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1295,41 +4557,41 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>163.49 ± 107.46</t>
+          <t>143.46 ± 107.90</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.60 ± 15.71</t>
+          <t>5.70 ± 10.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>143.65 ± 121.72</t>
+          <t>112.93 ± 108.21</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3.19 ± 17.94</t>
+          <t>0.17 ± 0.96</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>122.87 ± 101.97</t>
+          <t>144.85 ± 108.14</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3.80 ± 7.15</t>
+          <t>2.06 ± 4.19</t>
         </is>
       </c>
     </row>
@@ -1346,15 +4608,15 @@
         <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>69.85 ± 84.49</t>
+          <t>91.15 ± 92.28</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1363,41 +4625,41 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>180.03 ± 118.10</t>
+          <t>143.65 ± 108.09</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.00 ± 17.51</t>
+          <t>5.60 ± 8.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>142.27 ± 120.52</t>
+          <t>107.18 ± 106.38</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.19 ± 6.66</t>
+          <t>0.14 ± 0.62</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>123.47 ± 97.67</t>
+          <t>158.53 ± 119.80</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.9</v>
+        <v>0.66</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3.71 ± 5.43</t>
+          <t>3.21 ± 7.15</t>
         </is>
       </c>
     </row>
@@ -1412,11 +4674,11 @@
       <c r="D7" s="1" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>74.61 ± 89.28</t>
+          <t>79.02 ± 85.12</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
@@ -1425,41 +4687,41 @@
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>158.09 ± 114.81</t>
+          <t>142.79 ± 106.78</t>
         </is>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>8.79 ± 15.00</t>
+          <t>4.96 ± 8.93</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>124.81 ± 117.41</t>
+          <t>104.52 ± 103.93</t>
         </is>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>1.26 ± 9.40</t>
+          <t>0.13 ± 0.66</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>115.28 ± 101.17</t>
+          <t>145.99 ± 114.75</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>3.42 ± 6.48</t>
+          <t>2.58 ± 5.62</t>
         </is>
       </c>
     </row>
@@ -1474,7 +4736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1495,7 +4757,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Delta G</t>
+          <t>Delta Theta</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1530,38 +4792,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Goal Adapter Only</t>
+          <t>Avg Steps Global + Goal Adapter</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Goal Adapter Only</t>
+          <t>Success Prob Global + Goal Adapter</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Goal Adapter Only</t>
+          <t>Avg Viols Global + Goal Adapter</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Constraint Adapter Only</t>
+          <t>Avg Steps Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Constraint Adapter Only</t>
+          <t>Success Prob Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Constraint Adapter Only</t>
+          <t>Avg Viols Global + Constraint Adapter</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>6</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1569,395 +4833,123 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>163.40 ± 247.98</t>
+          <t>524.28 ± 417.07</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.05 ± 0.38</t>
+          <t>1.23 ± 4.67</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>489.13 ± 332.63</t>
+          <t>543.50 ± 418.39</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.83 ± 7.20</t>
+          <t>11.99 ± 17.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>185.93 ± 253.08</t>
+          <t>482.15 ± 438.15</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.88</v>
+        <v>0.61</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>1.57 ± 3.19</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>470.63 ± 341.56</t>
+          <t>548.59 ± 430.11</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>5.92 ± 11.29</t>
+          <t>11.38 ± 19.34</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>800</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>169.05 ± 211.19</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>506.70 ± 343.78</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>5.47 ± 9.97</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>168.12 ± 196.04</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>500.27 ± 336.00</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>6.77 ± 11.13</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>800</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>194.47 ± 239.02</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.02 ± 0.13</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>523.47 ± 347.28</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>5.53 ± 11.34</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>220.62 ± 249.21</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>475.58 ± 346.93</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>5.58 ± 11.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>800</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>221.15 ± 241.74</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>566.63 ± 313.51</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>3.22 ± 7.27</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>250.10 ± 262.09</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>589.18 ± 281.69</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>8.63 ± 27.14</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>800</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>270.28 ± 260.25</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>607.07 ± 284.87</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>3.07 ± 7.24</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>356.97 ± 304.80</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>610.98 ± 292.88</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2.98 ± 4.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>AVERAGE</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>203.67 ± 243.74</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>0.01 ± 0.18</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t>538.60 ± 328.04</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>4.42 ± 8.84</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>236.35 ± 263.96</t>
-        </is>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="M7" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="inlineStr">
-        <is>
-          <t>529.33 ± 326.34</t>
-        </is>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P7" s="1" t="inlineStr">
-        <is>
-          <t>5.98 ± 15.17</t>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>524.28 ± 417.07</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>1.23 ± 4.67</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>543.50 ± 418.39</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>11.99 ± 17.86</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>482.15 ± 438.15</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>1.57 ± 3.19</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>548.59 ± 430.11</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>11.38 ± 19.34</t>
         </is>
       </c>
     </row>
@@ -1972,7 +4964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1993,7 +4985,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Delta G</t>
+          <t>Delta Theta</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -2028,98 +5020,100 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Goal Adapter Only</t>
+          <t>Avg Steps Global + Goal Adapter</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Goal Adapter Only</t>
+          <t>Success Prob Global + Goal Adapter</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Goal Adapter Only</t>
+          <t>Avg Viols Global + Goal Adapter</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Constraint Adapter Only</t>
+          <t>Avg Steps Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Constraint Adapter Only</t>
+          <t>Success Prob Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Constraint Adapter Only</t>
+          <t>Avg Viols Global + Constraint Adapter</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B2" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="D2" t="n">
         <v>0.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>200.35 ± 176.95</t>
+          <t>365.10 ± 351.26</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.13 ± 0.69</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>319.98 ± 196.99</t>
+          <t>480.55 ± 318.44</t>
         </is>
       </c>
       <c r="I2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>12.42 ± 14.46</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>390.57 ± 341.98</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.33 ± 3.28</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>521.05 ± 330.71</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>0.52</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>11.41 ± 17.86</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>239.44 ± 201.14</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.13 ± 0.70</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>328.58 ± 200.86</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>0.49</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>5.33 ± 10.38</t>
+          <t>10.97 ± 20.33</t>
         </is>
       </c>
     </row>
@@ -2127,65 +5121,67 @@
       <c r="A3" t="n">
         <v>7</v>
       </c>
-      <c r="B3" t="n">
-        <v>5</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>258.21 ± 204.87</t>
+          <t>214.95 ± 280.24</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.68</v>
+        <v>0.85</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.02 ± 0.13</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>327.35 ± 197.81</t>
+          <t>463.37 ± 343.70</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14.88 ± 26.24</t>
+          <t>13.63 ± 19.18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>294.63 ± 203.43</t>
+          <t>262.25 ± 309.32</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.05 ± 0.41</t>
+          <t>1.53 ± 4.81</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>387.34 ± 181.04</t>
+          <t>424.97 ± 342.06</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.32</v>
+        <v>0.58</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>9.08 ± 16.84</t>
+          <t>11.40 ± 17.36</t>
         </is>
       </c>
     </row>
@@ -2193,325 +5189,265 @@
       <c r="A4" t="n">
         <v>8</v>
       </c>
-      <c r="B4" t="n">
-        <v>2</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="D4" t="n">
         <v>0.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>231.22 ± 196.96</t>
+          <t>335.32 ± 335.10</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.20 ± 1.29</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>264.53 ± 195.48</t>
+          <t>562.68 ± 293.87</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.67</v>
+        <v>0.45</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.57 ± 9.85</t>
+          <t>15.77 ± 25.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>247.12 ± 199.26</t>
+          <t>382.65 ± 313.21</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>3.37 ± 9.93</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>303.98 ± 194.66</t>
+          <t>569.75 ± 301.32</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.59</v>
+        <v>0.43</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.78 ± 6.27</t>
+          <t>14.82 ± 18.92</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="D5" t="n">
         <v>0.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>191.97 ± 180.07</t>
+          <t>361.62 ± 308.53</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.02 ± 0.13</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>316.98 ± 201.49</t>
+          <t>627.65 ± 268.25</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.12 ± 12.87</t>
+          <t>9.62 ± 13.14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>266.82 ± 205.58</t>
+          <t>373.83 ± 334.00</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>1.50 ± 6.85</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>321.68 ± 206.39</t>
+          <t>564.63 ± 302.66</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3.83 ± 7.66</t>
+          <t>10.00 ± 12.10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="D6" t="n">
         <v>0.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>260.52 ± 195.46</t>
+          <t>307.15 ± 297.47</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.02 ± 0.13</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>350.44 ± 177.39</t>
+          <t>540.23 ± 298.77</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.88 ± 16.94</t>
+          <t>8.27 ± 11.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>257.71 ± 206.49</t>
+          <t>453.27 ± 333.99</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.06 ± 0.60</t>
+          <t>0.77 ± 2.22</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>333.33 ± 200.39</t>
+          <t>568.43 ± 290.96</t>
         </is>
       </c>
       <c r="O6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>8.83 ± 17.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>316.83 ± 320.33</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>0.08 ± 0.67</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>534.90 ± 311.32</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
         <v>0.47</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>3.25 ± 6.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>500</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>227.85 ± 196.60</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>342.84 ± 191.83</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>11.94 ± 17.60</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>372.51 ± 332.55</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>1.70 ± 6.14</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>529.77 ± 319.00</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>0.49</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>6.74 ± 14.59</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>294.23 ± 202.20</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0.02 ± 0.20</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>336.50 ± 204.99</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>4.06 ± 21.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>AVERAGE</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>228.35 ± 193.82</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>320.35 ± 195.62</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>9.77 ± 17.41</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>266.66 ± 204.16</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="M8" s="1" t="inlineStr">
-        <is>
-          <t>0.04 ± 0.42</t>
-        </is>
-      </c>
-      <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>335.24 ± 199.88</t>
-        </is>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P8" s="1" t="inlineStr">
-        <is>
-          <t>4.72 ± 12.95</t>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>11.20 ± 17.67</t>
         </is>
       </c>
     </row>
@@ -2547,7 +5483,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Delta G</t>
+          <t>Delta Theta</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -2582,32 +5518,32 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Goal Adapter Only</t>
+          <t>Avg Steps Global + Goal Adapter</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Goal Adapter Only</t>
+          <t>Success Prob Global + Goal Adapter</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Goal Adapter Only</t>
+          <t>Avg Viols Global + Goal Adapter</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Constraint Adapter Only</t>
+          <t>Avg Steps Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Constraint Adapter Only</t>
+          <t>Success Prob Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Constraint Adapter Only</t>
+          <t>Avg Viols Global + Constraint Adapter</t>
         </is>
       </c>
     </row>
@@ -2628,11 +5564,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>163.30 ± 258.14</t>
+          <t>203.51 ± 300.02</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2641,41 +5577,41 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>498.40 ± 333.00</t>
+          <t>426.44 ± 334.18</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.88 ± 25.30</t>
+          <t>13.15 ± 19.87</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>338.56 ± 333.58</t>
+          <t>307.88 ± 319.81</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.09 ± 0.63</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>476.30 ± 345.28</t>
+          <t>371.23 ± 330.19</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>11.45 ± 20.97</t>
+          <t>11.69 ± 17.15</t>
         </is>
       </c>
     </row>
@@ -2696,54 +5632,54 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>160.06 ± 240.95</t>
+          <t>124.71 ± 205.94</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.02 ± 0.20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>525.70 ± 332.72</t>
+          <t>384.64 ± 327.01</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.06 ± 19.18</t>
+          <t>9.57 ± 15.09</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>379.15 ± 346.02</t>
+          <t>266.41 ± 319.26</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.06 ± 0.60</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>468.56 ± 342.89</t>
+          <t>408.15 ± 319.75</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>7.81 ± 15.68</t>
+          <t>10.49 ± 13.65</t>
         </is>
       </c>
     </row>
@@ -2764,54 +5700,54 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>163.41 ± 258.88</t>
+          <t>188.81 ± 232.61</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.01 ± 0.10</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>489.74 ± 338.45</t>
+          <t>427.04 ± 316.87</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12.34 ± 36.40</t>
+          <t>8.26 ± 10.04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>426.76 ± 345.51</t>
+          <t>421.73 ± 359.60</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.02 ± 0.20</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>506.51 ± 325.51</t>
+          <t>472.26 ± 328.29</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>7.99 ± 22.02</t>
+          <t>8.69 ± 12.28</t>
         </is>
       </c>
     </row>
@@ -2832,7 +5768,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>146.83 ± 216.63</t>
+          <t>193.41 ± 214.76</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2845,41 +5781,41 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>525.93 ± 328.31</t>
+          <t>457.14 ± 313.29</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.61 ± 14.50</t>
+          <t>9.84 ± 14.02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>519.26 ± 327.35</t>
+          <t>431.93 ± 338.98</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.05 ± 0.50</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>494.20 ± 342.16</t>
+          <t>437.86 ± 305.33</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.47</v>
+        <v>0.65</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>8.20 ± 32.25</t>
+          <t>9.47 ± 15.68</t>
         </is>
       </c>
     </row>
@@ -2900,54 +5836,54 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>173.13 ± 246.76</t>
+          <t>194.42 ± 238.25</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>0.06 ± 0.44</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>498.88 ± 297.18</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>10.22 ± 21.16</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>463.97 ± 355.42</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>565.61 ± 303.84</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>9.33 ± 42.06</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>452.83 ± 336.45</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>494.14 ± 335.40</t>
+          <t>520.88 ± 302.14</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6.78 ± 27.58</t>
+          <t>8.20 ± 17.20</t>
         </is>
       </c>
     </row>
@@ -2962,54 +5898,54 @@
       <c r="D7" s="1" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>161.35 ± 244.90</t>
+          <t>180.97 ± 242.28</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>0.00 ± 0.04</t>
+          <t>0.02 ± 0.22</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>521.08 ± 328.56</t>
+          <t>438.83 ± 320.20</t>
         </is>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>10.84 ± 29.48</t>
+          <t>10.21 ± 16.62</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>423.31 ± 343.50</t>
+          <t>378.38 ± 347.66</t>
         </is>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.04 ± 0.46</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>487.94 ± 338.60</t>
+          <t>442.08 ± 321.51</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>8.45 ± 24.43</t>
+          <t>9.71 ± 15.37</t>
         </is>
       </c>
     </row>
@@ -3024,6 +5960,982 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>267.58 ± 205.84</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>276.78 ± 198.82</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>12.80 ± 15.17</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>250.01 ± 198.23</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.11 ± 0.66</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>316.51 ± 191.84</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>12.48 ± 14.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>311.17 ± 200.15</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>384.61 ± 188.47</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>21.45 ± 22.92</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>322.51 ± 208.29</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.59 ± 2.28</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>382.58 ± 186.76</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>16.45 ± 21.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>219.59 ± 191.22</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>298.64 ± 191.20</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10.94 ± 13.47</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>256.22 ± 208.36</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.25 ± 1.14</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>249.39 ± 201.41</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>6.03 ± 8.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>269.12 ± 198.74</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>358.97 ± 181.69</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15.34 ± 14.19</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>308.06 ± 202.34</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.26 ± 1.10</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>325.37 ± 197.74</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>8.27 ± 11.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>237.81 ± 198.22</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>331.52 ± 189.66</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8.63 ± 11.77</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>263.62 ± 207.67</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.51</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>292.78 ± 198.00</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5.67 ± 15.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>320.87 ± 210.29</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.30</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>363.01 ± 190.63</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11.00 ± 12.72</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>316.81 ± 203.46</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.22 ± 1.29</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>383.09 ± 169.56</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>9.13 ± 13.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>271.02 ± 204.07</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.12</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>335.59 ± 193.85</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>13.36 ± 16.03</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>286.20 ± 206.97</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>0.25 ± 1.31</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>324.95 ± 196.99</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>9.67 ± 15.39</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>415.34 ± 433.33</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>23.24 ± 118.16</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>476.44 ± 407.18</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8.20 ± 25.97</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>404.04 ± 386.67</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>9.77 ± 31.78</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>532.30 ± 409.78</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>13.57 ± 42.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>451.77 ± 428.21</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>16.22 ± 98.04</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>487.38 ± 426.98</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7.40 ± 22.30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>425.20 ± 397.89</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>8.79 ± 49.85</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>507.72 ± 420.98</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>6.20 ± 35.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>492.48 ± 424.09</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>16.77 ± 79.12</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>529.21 ± 422.54</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7.52 ± 15.48</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>474.91 ± 409.84</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>8.00 ± 30.23</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>591.28 ± 413.22</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10.10 ± 26.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>508.78 ± 432.40</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8.15 ± 43.30</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>554.15 ± 415.16</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5.51 ± 14.61</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>564.53 ± 415.90</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6.28 ± 23.17</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>641.30 ± 405.90</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5.07 ± 20.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>467.09 ± 431.06</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>16.09 ± 89.20</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>511.80 ± 419.21</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>7.16 ± 20.18</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>467.17 ± 407.45</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>8.21 ± 35.19</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>568.15 ± 415.77</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>8.73 ± 32.40</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3045,7 +6957,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Delta G</t>
+          <t>Delta Theta</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -3080,32 +6992,32 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Goal Adapter Only</t>
+          <t>Avg Steps Global + Goal Adapter</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Goal Adapter Only</t>
+          <t>Success Prob Global + Goal Adapter</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Goal Adapter Only</t>
+          <t>Avg Viols Global + Goal Adapter</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps Constraint Adapter Only</t>
+          <t>Avg Steps Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob Constraint Adapter Only</t>
+          <t>Success Prob Global + Constraint Adapter</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols Constraint Adapter Only</t>
+          <t>Avg Viols Global + Constraint Adapter</t>
         </is>
       </c>
     </row>
@@ -3126,54 +7038,54 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>225.23 ± 370.53</t>
+          <t>223.71 ± 344.87</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.01 ± 0.10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>451.54 ± 437.50</t>
+          <t>475.04 ± 453.55</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24.07 ± 40.40</t>
+          <t>22.28 ± 40.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>568.55 ± 511.20</t>
+          <t>493.92 ± 460.79</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.09 ± 0.58</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>508.68 ± 487.33</t>
+          <t>539.31 ± 505.84</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>22.10 ± 37.78</t>
+          <t>26.51 ± 45.99</t>
         </is>
       </c>
     </row>
@@ -3194,7 +7106,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>231.96 ± 335.06</t>
+          <t>279.69 ± 371.48</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3202,46 +7114,46 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>0.08 ± 0.80</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>468.20 ± 432.02</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>17.71 ± 22.98</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>525.63 ± 475.16</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>496.82 ± 470.16</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>19.72 ± 28.28</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>604.09 ± 508.96</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.57 ± 5.67</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>574.93 ± 477.00</t>
+          <t>653.37 ± 502.96</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>25.87 ± 35.46</t>
+          <t>30.21 ± 52.88</t>
         </is>
       </c>
     </row>
@@ -3262,54 +7174,54 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>240.56 ± 326.11</t>
+          <t>266.42 ± 336.73</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>0.03 ± 0.22</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>492.22 ± 462.73</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>13.45 ± 22.39</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>653.60 ± 471.39</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>581.45 ± 490.33</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>15.10 ± 20.69</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>605.61 ± 528.23</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>636.29 ± 452.23</t>
+          <t>627.24 ± 501.63</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>17.16 ± 23.81</t>
+          <t>17.86 ± 32.29</t>
         </is>
       </c>
     </row>
@@ -3330,11 +7242,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>338.43 ± 395.72</t>
+          <t>326.14 ± 329.79</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3343,24 +7255,24 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>648.72 ± 466.42</t>
+          <t>667.82 ± 492.55</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11.45 ± 14.53</t>
+          <t>14.18 ± 24.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>673.58 ± 542.27</t>
+          <t>672.08 ± 503.40</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.51</v>
+        <v>0.59</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -3369,15 +7281,15 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>700.42 ± 463.24</t>
+          <t>719.10 ± 493.87</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>17.93 ± 26.57</t>
+          <t>15.50 ± 31.28</t>
         </is>
       </c>
     </row>
@@ -3398,33 +7310,33 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>356.32 ± 412.89</t>
+          <t>361.56 ± 365.78</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.05 ± 0.50</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>673.55 ± 458.41</t>
+          <t>682.59 ± 467.25</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11.05 ± 13.52</t>
+          <t>11.66 ± 19.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>731.11 ± 535.04</t>
+          <t>860.83 ± 463.11</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -3432,20 +7344,20 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.01 ± 0.10</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>737.14 ± 478.90</t>
+          <t>758.77 ± 462.47</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>14.93 ± 20.27</t>
+          <t>16.28 ± 33.97</t>
         </is>
       </c>
     </row>
@@ -3460,54 +7372,552 @@
       <c r="D7" s="1" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>278.50 ± 373.92</t>
+          <t>291.50 ± 353.37</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
+          <t>0.03 ± 0.43</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>557.17 ± 472.07</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>15.86 ± 27.10</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>641.21 ± 492.46</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.27</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>659.56 ± 499.44</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>21.27 ± 40.65</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML (Full)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>119.21 ± 112.80</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>128.23 ± 109.68</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8.28 ± 10.23</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>118.38 ± 112.45</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.06 ± 0.28</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>119.83 ± 108.14</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4.94 ± 8.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>105.25 ± 116.54</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>0.00 ± 0.00</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>123.40 ± 110.14</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7.61 ± 8.93</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>115.99 ± 110.67</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.13 ± 0.42</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>123.30 ± 104.43</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>6.28 ± 8.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>113.72 ± 114.94</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>140.13 ± 105.32</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9.57 ± 13.59</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>129.74 ± 119.35</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.06 ± 0.24</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>132.29 ± 107.67</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>6.55 ± 8.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>127.26 ± 113.05</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>129.45 ± 112.93</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10.22 ± 17.76</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>126.06 ± 113.85</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.26</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>151.97 ± 113.07</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>7.00 ± 10.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>107.52 ± 110.99</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>144.36 ± 106.28</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11.36 ± 13.24</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>105.32 ± 111.33</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.13 ± 0.63</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>150.30 ± 110.98</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>8.25 ± 14.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>114.59 ± 113.96</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.11</t>
+        </is>
+      </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>570.42 ± 472.65</t>
+          <t>133.11 ± 109.19</t>
         </is>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>16.28 ± 25.99</t>
+          <t>9.41 ± 13.18</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>636.59 ± 528.52</t>
+          <t>119.10 ± 113.89</t>
         </is>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>0.11 ± 2.55</t>
+          <t>0.09 ± 0.39</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>631.49 ± 479.10</t>
+          <t>135.54 ± 109.72</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>19.60 ± 29.81</t>
+          <t>6.60 ± 10.34</t>
         </is>
       </c>
     </row>

--- a/ablation_results.xlsx
+++ b/ablation_results.xlsx
@@ -458,17 +458,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1794,17 +1794,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -2292,17 +2292,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -2714,17 +2714,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -3268,17 +3268,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -3766,17 +3766,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -4762,17 +4762,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -4990,17 +4990,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -5488,17 +5488,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -5986,17 +5986,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -7460,17 +7460,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Avg Steps C-LAMAML (Full)</t>
+          <t>Avg Steps C-LAMAML</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Success Prob C-LAMAML (Full)</t>
+          <t>Success Prob C-LAMAML</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Viols C-LAMAML (Full)</t>
+          <t>Avg Viols C-LAMAML</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">

--- a/ablation_results.xlsx
+++ b/ablation_results.xlsx
@@ -9,6 +9,20 @@
   <sheets>
     <sheet name="ConstrainedGoToLocal_1c" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ConstrainedGoToObjDoor_1c" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ConstrainedActionObjDoor_1c" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ConstrainedOpenDoor_1c" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ConstrainedPickupDist_1c" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ConstrainedOpenDoorLoc_1c" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ConstrainedGoToOpen_1c" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ConstrainedOpenDoorsOrder_1c" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ConstrainedGoToObjDoor_2c" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ConstrainedGoToLocal_2c" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ConstrainedActionObjDoor_2c" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ConstrainedOpenDoor_2c" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ConstrainedPickupDist_2c" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ConstrainedOpenDoorLoc_2c" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ConstrainedGoToOpen_2c" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ConstrainedOpenDoorsOrder_2c" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -990,6 +1004,3396 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>139.23 ± 131.50</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>136.17 ± 123.73</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.36 ± 6.72</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>137.21 ± 132.04</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>154.04 ± 124.69</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.95 ± 5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>131.49 ± 137.69</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>129.84 ± 123.38</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.20 ± 7.51</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>139.33 ± 134.07</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>131.22 ± 128.89</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.15 ± 4.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>139.33 ± 126.37</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>122.93 ± 116.91</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.49 ± 1.20</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>139.71 ± 128.33</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>117.39 ± 115.51</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.48 ± 1.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>106.41 ± 124.17</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>147.82 ± 125.63</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1.32 ± 3.71</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>120.79 ± 128.38</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>116.02 ± 121.87</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.27 ± 3.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>120.50 ± 117.23</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>162.27 ± 123.26</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.56 ± 1.32</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>126.89 ± 122.52</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>140.80 ± 122.26</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.62 ± 2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>129.71 ± 122.69</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>153.90 ± 118.11</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.78 ± 2.16</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>135.24 ± 127.89</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>146.93 ± 118.84</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0.32 ± 1.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>127.78 ± 127.30</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>142.16 ± 122.65</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>0.95 ± 4.54</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>133.19 ± 129.11</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>134.40 ± 122.91</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>0.80 ± 3.23</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>540.77 ± 441.51</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>597.92 ± 427.40</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>29.27 ± 32.79</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>499.15 ± 454.44</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.16 ± 0.76</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>617.81 ± 431.60</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>27.42 ± 34.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>540.77 ± 441.51</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>597.92 ± 427.40</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>29.27 ± 32.79</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>499.15 ± 454.44</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>0.16 ± 0.76</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>617.81 ± 431.60</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>27.42 ± 34.14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>297.18 ± 313.54</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>571.90 ± 312.38</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>13.03 ± 23.54</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>297.73 ± 326.07</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>490.00 ± 333.02</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>8.75 ± 10.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>206.78 ± 259.84</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>503.90 ± 327.82</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>10.67 ± 20.78</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>228.17 ± 266.52</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>539.12 ± 320.17</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>22.72 ± 42.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>254.43 ± 285.23</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>583.62 ± 312.33</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>24.62 ± 47.13</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>254.77 ± 275.67</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>581.80 ± 330.57</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>15.78 ± 28.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>342.95 ± 287.00</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>638.80 ± 268.19</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>9.47 ± 17.63</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>307.40 ± 305.13</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>613.77 ± 287.39</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>13.88 ± 28.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>364.20 ± 301.10</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>549.10 ± 311.14</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>14.43 ± 40.92</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>318.95 ± 273.04</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>561.25 ± 312.15</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>13.95 ± 24.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>293.11 ± 295.54</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>569.46 ± 310.18</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>14.44 ± 32.67</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>281.40 ± 292.20</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>557.19 ± 319.81</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>15.02 ± 29.04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>278.27 ± 205.26</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>305.52 ± 188.61</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>17.92 ± 18.10</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>382.07 ± 200.28</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.17</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>323.29 ± 193.09</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>8.39 ± 15.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>325.07 ± 203.81</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>380.36 ± 177.94</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>23.95 ± 24.16</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>396.14 ± 190.31</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.24</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>375.52 ± 182.93</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>6.80 ± 12.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>269.30 ± 205.43</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>324.97 ± 180.38</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>17.49 ± 17.13</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>330.83 ± 217.87</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.12 ± 0.68</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>325.44 ± 205.14</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4.31 ± 6.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>321.00 ± 201.41</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>331.26 ± 194.11</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>17.64 ± 16.67</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>386.21 ± 192.35</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.31</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>354.95 ± 193.20</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>6.41 ± 13.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>308.40 ± 196.70</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>364.85 ± 174.67</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>12.63 ± 16.10</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>354.86 ± 212.70</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>358.86 ± 191.62</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3.87 ± 8.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>345.81 ± 191.11</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>371.08 ± 189.23</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>13.72 ± 14.81</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>389.24 ± 196.95</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>358.00 ± 192.56</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4.40 ± 9.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>307.98 ± 202.45</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>346.34 ± 186.29</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>17.23 ± 18.44</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>373.23 ± 203.30</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.34</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>349.34 ± 194.12</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>5.70 ± 11.32</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>262.72 ± 345.41</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.28</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>491.14 ± 354.24</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>23.83 ± 38.76</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>465.87 ± 352.18</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>478.55 ± 337.75</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>19.61 ± 27.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>169.66 ± 267.63</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.06 ± 0.60</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>478.03 ± 340.29</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>24.05 ± 33.20</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>430.46 ± 363.37</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>386.82 ± 347.07</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>18.02 ± 32.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>165.07 ± 253.01</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>463.46 ± 332.28</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>22.01 ± 31.54</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>539.64 ± 324.09</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.53 ± 5.27</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>466.19 ± 345.75</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>15.80 ± 20.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>172.99 ± 229.18</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>467.57 ± 317.68</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>20.54 ± 32.39</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>560.09 ± 327.16</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>399.09 ± 346.20</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>9.67 ± 17.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>191.96 ± 245.43</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>529.38 ± 323.74</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>12.39 ± 18.90</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>575.36 ± 323.55</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>498.61 ± 337.32</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>10.49 ± 17.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>192.48 ± 273.60</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.30</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>485.92 ± 334.74</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>20.56 ± 31.93</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>514.28 ± 343.12</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>0.11 ± 2.37</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>445.85 ± 345.73</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>14.72 ± 24.31</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>506.91 ± 455.27</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>41.24 ± 165.98</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>572.50 ± 441.63</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6.37 ± 22.41</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>538.03 ± 450.39</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>49.30 ± 149.06</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>616.34 ± 428.98</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3.25 ± 11.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>465.58 ± 444.84</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>26.95 ± 114.24</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>618.05 ± 444.83</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4.87 ± 14.03</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>526.60 ± 436.13</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>30.33 ± 117.71</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>612.28 ± 455.51</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.69 ± 5.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>654.00 ± 443.63</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>23.18 ± 92.78</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>611.84 ± 435.98</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>9.26 ± 33.62</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>651.30 ± 446.05</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>43.16 ± 98.78</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>751.20 ± 389.31</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4.40 ± 22.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>634.04 ± 441.48</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>30.07 ± 137.16</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>668.97 ± 430.25</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7.41 ± 31.85</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>702.04 ± 419.80</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>36.24 ± 109.32</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>764.16 ± 380.00</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>7.35 ± 39.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr"/>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>565.13 ± 453.54</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>30.36 ± 130.58</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>617.84 ± 439.55</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>6.98 ± 26.71</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>604.49 ± 444.54</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>39.76 ± 120.40</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>686.00 ± 420.75</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>4.17 ± 23.70</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>348.78 ± 465.26</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>583.76 ± 461.39</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>56.96 ± 60.61</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>390.99 ± 472.88</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>585.18 ± 468.02</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>69.80 ± 79.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>442.43 ± 496.15</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>595.98 ± 451.23</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>62.49 ± 67.33</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>405.72 ± 457.03</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>552.76 ± 472.36</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>55.00 ± 72.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>394.48 ± 444.23</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>608.06 ± 472.73</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>46.33 ± 46.23</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>361.60 ± 432.32</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>666.24 ± 468.76</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>52.08 ± 58.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>475.59 ± 452.03</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>666.49 ± 460.10</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>35.88 ± 35.63</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>369.26 ± 401.94</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>723.23 ± 474.28</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>36.65 ± 44.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>484.66 ± 469.99</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>728.70 ± 484.85</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>35.25 ± 35.42</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>489.08 ± 448.84</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>759.09 ± 476.66</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>32.92 ± 34.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>429.19 ± 468.67</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>636.60 ± 469.33</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>47.38 ± 51.90</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>403.33 ± 445.60</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>657.30 ± 478.53</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>49.29 ± 61.71</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1507,4 +4911,3335 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>533.60 ± 464.86</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.31</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>639.44 ± 418.42</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>16.98 ± 20.22</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>607.55 ± 456.19</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3.55 ± 18.65</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>639.29 ± 428.22</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>9.18 ± 14.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>533.60 ± 464.86</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.31</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>639.44 ± 418.42</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>16.98 ± 20.22</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>607.55 ± 456.19</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>3.55 ± 18.65</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>639.29 ± 428.22</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>9.18 ± 14.25</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>163.40 ± 247.98</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.38</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>489.13 ± 332.63</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4.83 ± 7.20</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>185.93 ± 253.08</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>470.63 ± 341.56</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5.92 ± 11.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>169.05 ± 211.19</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>506.70 ± 343.78</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5.47 ± 9.97</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>168.12 ± 196.04</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>500.27 ± 336.00</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>6.77 ± 11.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>194.47 ± 239.02</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.13</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>523.47 ± 347.28</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5.53 ± 11.34</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>220.62 ± 249.21</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>475.58 ± 346.93</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5.58 ± 11.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>221.15 ± 241.74</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>566.63 ± 313.51</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3.22 ± 7.27</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>250.10 ± 262.09</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>589.18 ± 281.69</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>8.63 ± 27.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>270.28 ± 260.25</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>607.07 ± 284.87</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3.07 ± 7.24</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>356.97 ± 304.80</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>610.98 ± 292.88</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2.98 ± 4.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>203.67 ± 243.74</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.18</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>538.60 ± 328.04</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>4.42 ± 8.84</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>236.35 ± 263.96</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>529.33 ± 326.34</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>5.98 ± 15.17</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>200.35 ± 176.95</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>319.98 ± 196.99</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>11.41 ± 17.86</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>239.44 ± 201.14</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.13 ± 0.70</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>328.58 ± 200.86</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5.33 ± 10.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>258.21 ± 204.87</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>327.35 ± 197.81</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>14.88 ± 26.24</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>294.63 ± 203.43</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.41</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>387.34 ± 181.04</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>9.08 ± 16.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>231.22 ± 196.96</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>264.53 ± 195.48</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6.57 ± 9.85</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>247.12 ± 199.26</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>303.98 ± 194.66</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.78 ± 6.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>191.97 ± 180.07</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>316.98 ± 201.49</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>9.12 ± 12.87</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>266.82 ± 205.58</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>321.68 ± 206.39</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3.83 ± 7.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>260.52 ± 195.46</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>350.44 ± 177.39</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>9.88 ± 16.94</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>257.71 ± 206.49</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.06 ± 0.60</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>333.33 ± 200.39</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3.25 ± 6.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>227.85 ± 196.60</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>342.84 ± 191.83</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6.74 ± 14.59</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>294.23 ± 202.20</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>336.50 ± 204.99</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4.06 ± 21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>228.35 ± 193.82</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>320.35 ± 195.62</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>9.77 ± 17.41</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>266.66 ± 204.16</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.42</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>335.24 ± 199.88</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>4.72 ± 12.95</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>163.30 ± 258.14</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>498.40 ± 333.00</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>14.88 ± 25.30</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>338.56 ± 333.58</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>476.30 ± 345.28</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>11.45 ± 20.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>160.06 ± 240.95</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>525.70 ± 332.72</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>10.06 ± 19.18</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>379.15 ± 346.02</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>468.56 ± 342.89</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>7.81 ± 15.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>163.41 ± 258.88</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>489.74 ± 338.45</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>12.34 ± 36.40</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>426.76 ± 345.51</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>506.51 ± 325.51</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>7.99 ± 22.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>146.83 ± 216.63</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>525.93 ± 328.31</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7.61 ± 14.50</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>519.26 ± 327.35</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>494.20 ± 342.16</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>8.20 ± 32.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>173.13 ± 246.76</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>565.61 ± 303.84</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>9.33 ± 42.06</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>452.83 ± 336.45</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>494.14 ± 335.40</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>6.78 ± 27.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>161.35 ± 244.90</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.04</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>521.08 ± 328.56</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>10.84 ± 29.48</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>423.31 ± 343.50</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>487.94 ± 338.60</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>8.45 ± 24.43</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>510.78 ± 452.81</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>17.84 ± 81.19</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>487.73 ± 401.51</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>16.01 ± 34.36</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>499.70 ± 438.03</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>19.50 ± 106.43</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>386.28 ± 380.45</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>10.64 ± 30.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>385.84 ± 416.83</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.88 ± 9.88</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>342.20 ± 357.27</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7.25 ± 17.37</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>435.56 ± 432.76</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3.47 ± 21.30</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>334.43 ± 360.26</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5.84 ± 25.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>664.19 ± 426.14</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>9.18 ± 53.10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>532.35 ± 412.51</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>10.76 ± 21.96</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>692.86 ± 428.32</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>18.19 ± 67.17</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>494.52 ± 413.04</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>6.74 ± 15.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>683.17 ± 433.52</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>12.55 ± 91.43</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>549.82 ± 429.54</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>8.35 ± 25.02</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>647.95 ± 443.58</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2.13 ± 7.27</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>488.02 ± 427.33</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5.43 ± 14.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr"/>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>561.00 ± 449.19</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>10.36 ± 67.09</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>478.02 ± 409.32</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>10.59 ± 25.67</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>569.02 ± 448.20</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>10.82 ± 64.43</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>425.81 ± 401.95</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>7.16 ± 22.63</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>225.23 ± 370.53</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>451.54 ± 437.50</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>24.07 ± 40.40</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>568.55 ± 511.20</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>508.68 ± 487.33</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>22.10 ± 37.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>231.96 ± 335.06</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>496.82 ± 470.16</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>19.72 ± 28.28</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>604.09 ± 508.96</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.57 ± 5.67</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>574.93 ± 477.00</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.87 ± 35.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>240.56 ± 326.11</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>581.45 ± 490.33</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>15.10 ± 20.69</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>605.61 ± 528.23</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>636.29 ± 452.23</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>17.16 ± 23.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>338.43 ± 395.72</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>648.72 ± 466.42</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>11.45 ± 14.53</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>673.58 ± 542.27</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>700.42 ± 463.24</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>17.93 ± 26.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>356.32 ± 412.89</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>673.55 ± 458.41</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>11.05 ± 13.52</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>731.11 ± 535.04</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>737.14 ± 478.90</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>14.93 ± 20.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>278.50 ± 373.92</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>570.42 ± 472.65</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>16.28 ± 25.99</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>636.59 ± 528.52</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>0.11 ± 2.55</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>631.49 ± 479.10</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>19.60 ± 29.81</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>80.02 ± 87.28</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>101.64 ± 102.11</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.07 ± 0.35</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>93.97 ± 93.48</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>93.94 ± 93.67</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.12 ± 0.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>90.20 ± 99.24</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>103.23 ± 102.54</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.40</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>70.85 ± 91.05</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>86.18 ± 96.49</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.12 ± 0.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>100.63 ± 106.94</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>95.50 ± 97.14</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.21 ± 0.83</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>92.55 ± 104.75</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>120.06 ± 109.62</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.12 ± 0.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>94.48 ± 98.84</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>96.28 ± 94.73</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.16 ± 0.70</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>93.02 ± 104.74</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>109.81 ± 104.20</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.20 ± 0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>107.22 ± 109.23</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>113.19 ± 108.58</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.31 ± 1.12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>94.51 ± 103.35</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>111.03 ± 108.25</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.24 ± 0.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>94.51 ± 101.02</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>101.97 ± 101.34</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>0.17 ± 0.74</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>88.98 ± 100.07</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>104.20 ± 103.38</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>0.16 ± 0.63</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/ablation_results.xlsx
+++ b/ablation_results.xlsx
@@ -4919,7 +4919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5142,6 +5142,236 @@
       <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>9.18 ± 14.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: delta_g=0.7, delta_c=0.3 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>398.66 ± 404.94</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>688.18 ± 403.75</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>19.45 ± 21.40</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>392.06 ± 413.65</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>550.21 ± 425.32</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>11.83 ± 15.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>398.66 ± 404.94</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>688.18 ± 403.75</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>19.45 ± 21.40</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>392.06 ± 413.65</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>550.21 ± 425.32</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>11.83 ± 15.41</t>
         </is>
       </c>
     </row>

--- a/ablation_results.xlsx
+++ b/ablation_results.xlsx
@@ -4919,7 +4919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5027,58 +5027,58 @@
         <v>0.7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>533.60 ± 464.86</t>
+          <t>398.66 ± 404.94</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.52</v>
+        <v>0.75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.04 ± 0.31</t>
+          <t>0.01 ± 0.10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>639.44 ± 418.42</t>
+          <t>688.18 ± 403.75</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>16.98 ± 20.22</t>
+          <t>19.45 ± 21.40</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>607.55 ± 456.19</t>
+          <t>392.06 ± 413.65</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.45</v>
+        <v>0.73</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3.55 ± 18.65</t>
+          <t>0.02 ± 0.14</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>639.29 ± 428.22</t>
+          <t>550.21 ± 425.32</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>9.18 ± 14.25</t>
+          <t>11.83 ± 15.41</t>
         </is>
       </c>
     </row>
@@ -5094,282 +5094,52 @@
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>533.60 ± 464.86</t>
+          <t>398.66 ± 404.94</t>
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.52</v>
+        <v>0.75</v>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>0.04 ± 0.31</t>
+          <t>0.01 ± 0.10</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>639.44 ± 418.42</t>
+          <t>688.18 ± 403.75</t>
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>16.98 ± 20.22</t>
+          <t>19.45 ± 21.40</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>607.55 ± 456.19</t>
+          <t>392.06 ± 413.65</t>
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0.45</v>
+        <v>0.73</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>3.55 ± 18.65</t>
+          <t>0.02 ± 0.14</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>639.29 ± 428.22</t>
+          <t>550.21 ± 425.32</t>
         </is>
       </c>
       <c r="P3" s="1" t="n">
-        <v>0.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q3" s="1" t="inlineStr">
-        <is>
-          <t>9.18 ± 14.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>--- NEW RUN: delta_g=0.7, delta_c=0.3 ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Room Size</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Num Distractor</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Max Steps</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>Delta G</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>Delta C</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps C-LAMAML</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob C-LAMAML</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols C-LAMAML</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps Global Only</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob Global Only</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols Global Only</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps Global + Goal Adapter</t>
-        </is>
-      </c>
-      <c r="M6" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob Global + Goal Adapter</t>
-        </is>
-      </c>
-      <c r="N6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols Global + Goal Adapter</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps Global + Constraint Adapter</t>
-        </is>
-      </c>
-      <c r="P6" s="1" t="inlineStr">
-        <is>
-          <t>Success Prob Global + Constraint Adapter</t>
-        </is>
-      </c>
-      <c r="Q6" s="1" t="inlineStr">
-        <is>
-          <t>Avg Viols Global + Constraint Adapter</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>398.66 ± 404.94</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.01 ± 0.10</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>688.18 ± 403.75</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>19.45 ± 21.40</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>392.06 ± 413.65</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.02 ± 0.14</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>550.21 ± 425.32</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>11.83 ± 15.41</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>AVERAGE</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
-      <c r="D8" s="1" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr"/>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>398.66 ± 404.94</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>0.01 ± 0.10</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>688.18 ± 403.75</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>19.45 ± 21.40</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>392.06 ± 413.65</t>
-        </is>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>0.02 ± 0.14</t>
-        </is>
-      </c>
-      <c r="O8" s="1" t="inlineStr">
-        <is>
-          <t>550.21 ± 425.32</t>
-        </is>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="Q8" s="1" t="inlineStr">
         <is>
           <t>11.83 ± 15.41</t>
         </is>

--- a/ablation_results.xlsx
+++ b/ablation_results.xlsx
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1574,6 +1574,1148 @@
       <c r="Q8" s="1" t="inlineStr">
         <is>
           <t>0.80 ± 3.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: delta_g=0.3, delta_c=0.1 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>139.23 ± 131.50</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>136.17 ± 123.73</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1.36 ± 6.72</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>137.21 ± 132.04</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>154.04 ± 124.69</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.95 ± 5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>131.49 ± 137.69</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>129.84 ± 123.38</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1.20 ± 7.51</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>139.33 ± 134.07</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>131.22 ± 128.89</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.15 ± 4.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>139.33 ± 126.37</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>122.93 ± 116.91</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.49 ± 1.20</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>139.71 ± 128.33</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>117.39 ± 115.51</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.48 ± 1.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>106.41 ± 124.17</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>147.82 ± 125.63</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1.32 ± 3.71</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>120.79 ± 128.38</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>116.02 ± 121.87</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.27 ± 3.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>120.50 ± 117.23</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>162.27 ± 123.26</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.56 ± 1.32</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>126.89 ± 122.52</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>140.80 ± 122.26</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0.62 ± 2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>300</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>129.71 ± 122.69</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>153.90 ± 118.11</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.78 ± 2.16</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>135.24 ± 127.89</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>146.93 ± 118.84</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0.32 ± 1.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>127.78 ± 127.30</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>142.16 ± 122.65</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>0.95 ± 4.54</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>133.19 ± 129.11</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O18" s="1" t="inlineStr">
+        <is>
+          <t>134.40 ± 122.91</t>
+        </is>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="Q18" s="1" t="inlineStr">
+        <is>
+          <t>0.80 ± 3.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: delta_g=0.5, delta_c=0.3 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M21" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P21" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>300</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>147.69 ± 137.44</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>115.89 ± 111.79</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>24.34 ± 36.59</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>128.04 ± 129.18</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0.10 ± 0.50</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>129.71 ± 119.50</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>19.86 ± 38.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>300</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>135.61 ± 137.62</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>119.27 ± 115.80</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>24.68 ± 43.14</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>121.70 ± 130.05</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0.68 ± 6.47</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>139.01 ± 121.39</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>20.83 ± 36.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>300</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>137.54 ± 128.19</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>131.58 ± 112.86</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>21.16 ± 28.33</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>138.39 ± 124.99</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0.18 ± 0.96</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>149.99 ± 115.77</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>21.21 ± 31.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>300</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>125.06 ± 127.68</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>159.74 ± 126.23</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>22.97 ± 35.58</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>99.33 ± 114.35</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.72</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>165.48 ± 120.02</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>15.83 ± 22.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>300</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>100.99 ± 110.26</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>166.52 ± 117.71</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>24.56 ± 35.40</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>140.93 ± 120.34</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.22</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>175.71 ± 113.49</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>16.65 ± 24.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>123.66 ± 123.17</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>162.81 ± 117.57</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>20.34 ± 26.13</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>124.30 ± 125.37</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>164.69 ± 123.20</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>15.27 ± 20.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr"/>
+      <c r="D28" s="1" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr"/>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>128.43 ± 128.57</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>142.63 ± 118.96</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>23.01 ± 34.69</t>
+        </is>
+      </c>
+      <c r="L28" s="1" t="inlineStr">
+        <is>
+          <t>125.45 ± 124.91</t>
+        </is>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N28" s="1" t="inlineStr">
+        <is>
+          <t>0.18 ± 2.71</t>
+        </is>
+      </c>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t>154.10 ± 120.02</t>
+        </is>
+      </c>
+      <c r="P28" s="1" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q28" s="1" t="inlineStr">
+        <is>
+          <t>18.27 ± 29.86</t>
         </is>
       </c>
     </row>

--- a/ablation_results.xlsx
+++ b/ablation_results.xlsx
@@ -2730,7 +2730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2951,6 +2951,466 @@
         <v>0.48</v>
       </c>
       <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>27.42 ± 34.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: delta_g=0.7, delta_c=0.3 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>540.77 ± 441.51</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>597.92 ± 427.40</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>29.27 ± 32.79</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>499.15 ± 454.44</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.16 ± 0.76</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>617.81 ± 431.60</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>27.42 ± 34.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>540.77 ± 441.51</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>597.92 ± 427.40</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>29.27 ± 32.79</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>499.15 ± 454.44</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>0.16 ± 0.76</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>617.81 ± 431.60</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>27.42 ± 34.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: delta_g=0.7, delta_c=0.3 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>540.77 ± 441.51</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>597.92 ± 427.40</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>29.27 ± 32.79</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>499.15 ± 454.44</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.16 ± 0.76</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>617.81 ± 431.60</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>27.42 ± 34.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr"/>
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>540.77 ± 441.51</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>597.92 ± 427.40</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>29.27 ± 32.79</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>499.15 ± 454.44</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>0.16 ± 0.76</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>617.81 ± 431.60</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q13" s="1" t="inlineStr">
         <is>
           <t>27.42 ± 34.14</t>
         </is>

--- a/ablation_results.xlsx
+++ b/ablation_results.xlsx
@@ -6521,7 +6521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6742,6 +6742,236 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>11.83 ± 15.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: delta_g=0.7, delta_c=0.3 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Delta G</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Delta C</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global Only</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global Only</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global Only</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Goal Adapter</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Global + Constraint Adapter</t>
+        </is>
+      </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Global + Constraint Adapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>398.66 ± 404.94</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>688.18 ± 403.75</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>19.45 ± 21.40</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>392.06 ± 413.65</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>550.21 ± 425.32</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>11.83 ± 15.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>398.66 ± 404.94</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>688.18 ± 403.75</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>19.45 ± 21.40</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>392.06 ± 413.65</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>550.21 ± 425.32</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
         <is>
           <t>11.83 ± 15.41</t>
         </is>
